--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104487_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104487_W4.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7022</v>
+        <v>5.173</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5759</v>
+        <v>3.8576</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1262</v>
+        <v>1.3155</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3196</v>
+        <v>2.3262</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0273</v>
+        <v>0.0368</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2923</v>
+        <v>2.2894</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6889</v>
+        <v>2.6662</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3693</v>
+        <v>-0.34</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2979</v>
+        <v>0.1639</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0212</v>
+        <v>0.3295</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3191</v>
+        <v>-0.1656</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5709</v>
+        <v>3.3951</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0235</v>
+        <v>5.0062</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4526</v>
+        <v>-1.6111</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4989</v>
+        <v>3.5051</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1789</v>
+        <v>3.1739</v>
       </c>
       <c r="I3" t="n">
-        <v>0.32</v>
+        <v>0.3312</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1082</v>
+        <v>4.09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8097</v>
+        <v>3.7921</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.5849</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.369</v>
+        <v>0.3714</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2704</v>
+        <v>-0.4618</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4529</v>
+        <v>2.9914</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4937</v>
+        <v>2.2405</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.7509</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9978</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0404</v>
+        <v>1.037</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0426</v>
+        <v>-0.0385</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4773</v>
+        <v>1.4707</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4027</v>
+        <v>1.3962</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4795</v>
+        <v>-0.4722</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1091</v>
+        <v>0.6562</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5777</v>
+        <v>0.3436</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5314</v>
+        <v>0.3126</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7905</v>
+        <v>2.6734</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6345</v>
+        <v>3.2011</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.844</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7975</v>
+        <v>1.0961</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5758</v>
+        <v>0.327</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7784</v>
+        <v>0.7691</v>
       </c>
       <c r="J5" t="n">
-        <v>2.625</v>
+        <v>2.7692</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5211</v>
+        <v>0.7584</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1038</v>
+        <v>2.0108</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8275</v>
+        <v>-1.6731</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9453</v>
+        <v>-0.4314</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8822</v>
+        <v>-1.2417</v>
       </c>
       <c r="P5" t="n">
+        <v>2.0487</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.361</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>1.286</v>
+        <v>0.6181</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6635</v>
+        <v>0.4319</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3775</v>
+        <v>0.1862</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7071</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4549</v>
+        <v>2.3254</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5205</v>
+        <v>4.3037</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0656</v>
+        <v>-1.9783</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4082</v>
+        <v>4.3868</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.427</v>
+        <v>-0.4361</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8352</v>
+        <v>4.8228</v>
       </c>
       <c r="J6" t="n">
-        <v>6.4198</v>
+        <v>6.3757</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1425</v>
+        <v>-0.1626</v>
       </c>
       <c r="L6" t="n">
-        <v>6.5623</v>
+        <v>6.5384</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0116</v>
+        <v>-1.989</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.046</v>
+        <v>-0.1509</v>
       </c>
       <c r="T6" t="n">
-        <v>0.369</v>
+        <v>0.2042</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.415</v>
+        <v>-0.3551</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9241</v>
+        <v>1.8411</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3597</v>
+        <v>2.722</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4355</v>
+        <v>-0.8809</v>
       </c>
       <c r="G7" t="n">
-        <v>1.08</v>
+        <v>0.7879</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3202</v>
+        <v>1.5686</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7598</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.777</v>
+        <v>2.5913</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7619</v>
+        <v>2.5026</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0151</v>
+        <v>0.0887</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6971</v>
+        <v>-1.8034</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4417</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2554</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>-1.3658</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3658</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.4433</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.0415</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.1047</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.4174</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.3127</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.0927</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.0927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1179</v>
+        <v>1.087</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0349</v>
+        <v>0.0893</v>
       </c>
       <c r="F8" t="n">
-        <v>0.083</v>
+        <v>0.9977</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2424</v>
+        <v>0.7488</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6667</v>
+        <v>2.3666</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5758</v>
+        <v>-1.6178</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1213</v>
+        <v>1.0046</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3133</v>
+        <v>3.344</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.192</v>
+        <v>-2.3394</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1211</v>
+        <v>-0.2558</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.9774</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7678</v>
+        <v>0.7215</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.849</v>
+        <v>0.3869</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1553</v>
+        <v>0.2715</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3064</v>
+        <v>0.1154</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0373</v>
+        <v>-0.0031</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8363</v>
+        <v>-0.5239</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8736</v>
+        <v>0.5208</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7511</v>
+        <v>2.2396</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3664</v>
+        <v>1.6631</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6153</v>
+        <v>0.5765</v>
       </c>
       <c r="J9" t="n">
-        <v>1.035</v>
+        <v>2.0942</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3594</v>
+        <v>2.2958</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.3245</v>
+        <v>-0.2015</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2839</v>
+        <v>0.1454</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.993</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7091</v>
+        <v>0.778</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6723</v>
+        <v>0.7376</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6956</v>
+        <v>0.6385</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0233</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1267</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1076</v>
+        <v>-1.0251</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0191</v>
+        <v>0.0327</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8278</v>
+        <v>0.8156</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6061</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4339</v>
+        <v>1.4189</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0882</v>
+        <v>1.0586</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9221</v>
+        <v>0.9002</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2603</v>
+        <v>-0.243</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.206</v>
+        <v>-0.0569</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2994</v>
+        <v>0.4202</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5054</v>
+        <v>-0.4771</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.817</v>
+        <v>-2.1218</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6572</v>
+        <v>-0.7716</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1597</v>
+        <v>-1.3502</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5849</v>
+        <v>-0.5819</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0807</v>
+        <v>-1.0827</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4958</v>
+        <v>0.5007</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0168</v>
+        <v>0.0045</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6017</v>
+        <v>-0.5865</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7945</v>
+        <v>0.4798</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>0.2042</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4951</v>
+        <v>0.2755</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3736</v>
+        <v>-3.9498</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5897</v>
+        <v>-3.2478</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.702</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2003</v>
+        <v>-0.183</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6555</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4665</v>
+        <v>0.4725</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2332</v>
+        <v>0.2324</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4335</v>
+        <v>-0.4154</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8142</v>
+        <v>-0.3995</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2577</v>
+        <v>-0.1972</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.7334</v>
+        <v>12.4193</v>
       </c>
       <c r="E13" t="n">
-        <v>15.4519</v>
+        <v>15.852</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7183</v>
+        <v>-3.4326</v>
       </c>
       <c r="G13" t="n">
-        <v>16.1381</v>
+        <v>16.1397</v>
       </c>
       <c r="H13" t="n">
-        <v>7.395099999999999</v>
+        <v>7.395400000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>8.742999999999999</v>
+        <v>8.7441</v>
       </c>
       <c r="J13" t="n">
-        <v>24.5907</v>
+        <v>24.3574</v>
       </c>
       <c r="K13" t="n">
-        <v>14.4892</v>
+        <v>14.3673</v>
       </c>
       <c r="L13" t="n">
-        <v>10.1013</v>
+        <v>9.990399999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.4527</v>
+        <v>-8.2179</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.093900000000001</v>
+        <v>-6.971500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3586</v>
+        <v>-1.2462</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.5367</v>
+        <v>-4.552700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0125</v>
+        <v>-17.0723</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9961</v>
+        <v>2.6955</v>
       </c>
       <c r="T13" t="n">
-        <v>3.085</v>
+        <v>3.806699999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.089</v>
+        <v>-1.1113</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W13" t="n">
-        <v>4.7887</v>
+        <v>4.759899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.6525</v>
+        <v>-6.6231</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6141</v>
+        <v>4.2233</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7468</v>
+        <v>5.2934</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1327</v>
+        <v>-1.0701</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2885</v>
+        <v>2.2804</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4863</v>
+        <v>-0.4854</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7747</v>
+        <v>2.7658</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4623</v>
+        <v>4.4285</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9626</v>
+        <v>0.9513</v>
       </c>
       <c r="L14" t="n">
-        <v>3.4997</v>
+        <v>3.4773</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1738</v>
+        <v>-2.1481</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3814</v>
+        <v>0.2404</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3811</v>
+        <v>0.2111</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0003</v>
+        <v>0.0294</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5727</v>
+        <v>3.2282</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4964</v>
+        <v>4.9991</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9237</v>
+        <v>-1.7709</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0541</v>
+        <v>0.0516</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4589</v>
+        <v>1.4563</v>
       </c>
       <c r="I15" t="n">
         <v>-1.4047</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4521</v>
+        <v>2.4302</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7187</v>
+        <v>2.7062</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.398</v>
+        <v>-2.3786</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4525</v>
+        <v>0.1067</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0858</v>
+        <v>0.6176</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6333</v>
+        <v>-0.5108</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3798</v>
+        <v>2.3194</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7309</v>
+        <v>2.7028</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.351</v>
+        <v>-0.3834</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5516</v>
+        <v>-0.546</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0076</v>
+        <v>-1.0054</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3904</v>
+        <v>1.3732</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.942</v>
+        <v>-1.9193</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0931</v>
+        <v>-0.1557</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0302</v>
+        <v>-0.0283</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0629</v>
+        <v>-0.1275</v>
       </c>
       <c r="V16" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7173</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6197</v>
+        <v>0.7624</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0963</v>
+        <v>0.1036</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1516</v>
+        <v>-0.1467</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2479</v>
+        <v>0.2504</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2185</v>
+        <v>0.2179</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1222</v>
+        <v>-0.1143</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2825</v>
+        <v>-0.1579</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1615</v>
+        <v>-0.037</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1281</v>
+        <v>-0.4494</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3072</v>
+        <v>1.0026</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1791</v>
+        <v>-1.452</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9017</v>
+        <v>0.4787</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4704</v>
+        <v>-0.5343</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4313</v>
+        <v>1.0131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8853</v>
+        <v>2.5848</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9626</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.668</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.787</v>
+        <v>-2.1061</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.433</v>
+        <v>-1.4511</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.354</v>
+        <v>-0.6549</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
+        <v>-1.3658</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2763</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.2045</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.2164</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.6342</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.1342</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.7349</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.2612</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.5263</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.1607</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1607</v>
-      </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1566</v>
+        <v>-0.4541</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1438</v>
+        <v>1.7025</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3004</v>
+        <v>-2.1566</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4734</v>
+        <v>-1.8963</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.471</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0103</v>
+        <v>-1.4253</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6045</v>
+        <v>0.8691</v>
       </c>
       <c r="K19" t="n">
-        <v>0.928</v>
+        <v>0.9513</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6765</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1311</v>
+        <v>-2.7654</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4648</v>
+        <v>-1.4223</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6663</v>
+        <v>-1.3432</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1016</v>
+        <v>0.1462</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0998</v>
+        <v>0.6756</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2014</v>
+        <v>-0.5294</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.639</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9262</v>
+        <v>-2.1183</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6907</v>
+        <v>0.4426</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6169</v>
+        <v>-2.5609</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1326</v>
+        <v>-1.1246</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7489</v>
+        <v>-0.7496</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3838</v>
+        <v>-0.375</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2653</v>
+        <v>1.254</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.398</v>
+        <v>-2.3786</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4171</v>
+        <v>-1.4078</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0638</v>
+        <v>-0.2685</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1966</v>
+        <v>-0.0375</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0512</v>
+        <v>-3.1797</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8562</v>
+        <v>-2.0086</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.195</v>
+        <v>-1.1711</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8706</v>
+        <v>-0.8731</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5151</v>
+        <v>1.5164</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3857</v>
+        <v>-2.3895</v>
       </c>
       <c r="J21" t="n">
-        <v>1.386</v>
+        <v>1.362</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4763</v>
+        <v>2.4649</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2566</v>
+        <v>-2.2351</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1391</v>
+        <v>-0.2579</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3871</v>
+        <v>0.2715</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5263</v>
+        <v>-0.5294</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5211</v>
+        <v>-3.3227</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0217</v>
+        <v>-0.5716</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4994</v>
+        <v>-2.7511</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4825</v>
+        <v>-2.4783</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9365</v>
+        <v>-0.9336</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.546</v>
+        <v>-1.5447</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4936</v>
+        <v>0.474</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6856</v>
+        <v>0.6755</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9761</v>
+        <v>-2.9522</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3995</v>
+        <v>-0.2102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3811</v>
+        <v>0.0926</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0185</v>
+        <v>-0.3028</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9874</v>
+        <v>-3.8858</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.855</v>
+        <v>-2.9081</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1324</v>
+        <v>-0.9776</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.9167</v>
+        <v>-4.9413</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.2014</v>
+        <v>-6.2254</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2848</v>
+        <v>1.284</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2551</v>
+        <v>-2.305</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.2648</v>
+        <v>-4.3004</v>
       </c>
       <c r="L23" t="n">
-        <v>2.0097</v>
+        <v>1.9955</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6615</v>
+        <v>-2.6364</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9366</v>
+        <v>-1.9249</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2976</v>
+        <v>-0.1721</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0121</v>
+        <v>-0.0097</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2855</v>
+        <v>-0.1623</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.5032</v>
+        <v>-8.942399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.7621</v>
+        <v>-7.3191</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7411</v>
+        <v>-1.6233</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.1946</v>
+        <v>-7.1944</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2931</v>
+        <v>-1.2816</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.9016</v>
+        <v>-5.9128</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.4503</v>
+        <v>-4.471</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.6062</v>
+        <v>-4.6261</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7443</v>
+        <v>-2.7233</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.628</v>
+        <v>-1.0652</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8166</v>
+        <v>-0.3441</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8115</v>
+        <v>-0.721</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.7337</v>
+        <v>-11.7221</v>
       </c>
       <c r="E25" t="n">
-        <v>3.718399999999999</v>
+        <v>3.4326</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.452</v>
+        <v>-15.1546</v>
       </c>
       <c r="G25" t="n">
-        <v>-16.138</v>
+        <v>-16.1397</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.395099999999999</v>
+        <v>-7.3956</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.743</v>
+        <v>-8.7441</v>
       </c>
       <c r="J25" t="n">
-        <v>8.4526</v>
+        <v>8.217700000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>7.094099999999999</v>
+        <v>6.971600000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3586</v>
+        <v>1.2464</v>
       </c>
       <c r="M25" t="n">
-        <v>-24.5906</v>
+        <v>-24.3574</v>
       </c>
       <c r="N25" t="n">
-        <v>-14.4892</v>
+        <v>-14.367</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.1015</v>
+        <v>-9.9903</v>
       </c>
       <c r="P25" t="n">
-        <v>4.536799999999999</v>
+        <v>4.5528</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4759</v>
+        <v>-12.5198</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0126</v>
+        <v>17.0726</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.996</v>
+        <v>-1.9987</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0888</v>
+        <v>1.1115</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0851</v>
+        <v>-3.1098</v>
       </c>
       <c r="V25" t="n">
-        <v>1.8639</v>
+        <v>1.8633</v>
       </c>
       <c r="W25" t="n">
-        <v>6.6525</v>
+        <v>6.6232</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.7887</v>
+        <v>-4.7598</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104487_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104487_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.6231</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104487_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.7598</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
